--- a/docs/詳細設計書/テーブル定義書.xlsx
+++ b/docs/詳細設計書/テーブル定義書.xlsx
@@ -461,12 +461,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -499,19 +499,17 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo UI"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -524,14 +522,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -546,7 +536,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -560,22 +557,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -586,6 +568,14 @@
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -605,7 +595,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -620,22 +642,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -644,7 +650,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -671,97 +677,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -779,13 +707,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -797,19 +731,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,7 +773,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -839,7 +797,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -905,15 +911,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -953,15 +950,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -973,6 +961,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1010,19 +1016,19 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1034,125 +1040,125 @@
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1210,6 +1216,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1225,7 +1237,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1583,22 +1595,22 @@
   <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="3.77777777777778" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="3.77777777777778" style="28"/>
-    <col min="2" max="2" width="5.11111111111111" style="29" customWidth="1"/>
-    <col min="3" max="3" width="12.2222222222222" style="28" customWidth="1"/>
-    <col min="4" max="4" width="6.88888888888889" style="28" customWidth="1"/>
-    <col min="5" max="5" width="66.1111111111111" style="28" customWidth="1"/>
-    <col min="6" max="16384" width="3.77777777777778" style="28"/>
+    <col min="1" max="1" width="3.77777777777778" style="30"/>
+    <col min="2" max="2" width="5.11111111111111" style="31" customWidth="1"/>
+    <col min="3" max="3" width="12.2222222222222" style="30" customWidth="1"/>
+    <col min="4" max="4" width="6.88888888888889" style="30" customWidth="1"/>
+    <col min="5" max="5" width="66.1111111111111" style="30" customWidth="1"/>
+    <col min="6" max="16384" width="3.77777777777778" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" s="28" customFormat="1" spans="1:2">
-      <c r="A1" s="28" t="s">
+    <row r="1" s="30" customFormat="1" spans="1:2">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-    </row>
-    <row r="2" s="28" customFormat="1" spans="2:5">
-      <c r="B2" s="30" t="s">
+      <c r="B1" s="31"/>
+    </row>
+    <row r="2" s="30" customFormat="1" spans="2:5">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="15" t="s">
@@ -1611,417 +1623,417 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" s="28" customFormat="1" spans="2:5">
-      <c r="B3" s="31" t="s">
+    <row r="3" s="30" customFormat="1" spans="2:5">
+      <c r="B3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="34">
         <v>45636</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="35" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="28" customFormat="1" ht="66" spans="2:5">
-      <c r="B4" s="31" t="s">
+    <row r="4" s="30" customFormat="1" ht="66" spans="2:5">
+      <c r="B4" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="34">
         <v>45733</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="28" customFormat="1" spans="2:5">
-      <c r="B5" s="31"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-    </row>
-    <row r="6" s="28" customFormat="1" spans="2:5">
-      <c r="B6" s="31"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-    </row>
-    <row r="7" s="28" customFormat="1" spans="2:5">
-      <c r="B7" s="31"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-    </row>
-    <row r="8" s="28" customFormat="1" spans="2:5">
-      <c r="B8" s="31"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-    </row>
-    <row r="9" s="28" customFormat="1" spans="2:5">
-      <c r="B9" s="31"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" s="28" customFormat="1" spans="2:5">
-      <c r="B10" s="31"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-    </row>
-    <row r="11" s="28" customFormat="1" spans="2:5">
-      <c r="B11" s="31"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-    </row>
-    <row r="12" s="28" customFormat="1" spans="2:5">
-      <c r="B12" s="31"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-    </row>
-    <row r="13" s="28" customFormat="1" spans="2:5">
-      <c r="B13" s="31"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-    </row>
-    <row r="14" s="28" customFormat="1" spans="2:5">
-      <c r="B14" s="31"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-    </row>
-    <row r="15" s="28" customFormat="1" spans="2:5">
-      <c r="B15" s="31"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-    </row>
-    <row r="16" s="28" customFormat="1" spans="2:5">
-      <c r="B16" s="31"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-    </row>
-    <row r="17" s="28" customFormat="1" spans="2:5">
-      <c r="B17" s="31"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-    </row>
-    <row r="18" s="28" customFormat="1" spans="2:5">
-      <c r="B18" s="31"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-    </row>
-    <row r="19" s="28" customFormat="1" spans="2:5">
-      <c r="B19" s="31"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-    </row>
-    <row r="20" s="28" customFormat="1" spans="2:5">
-      <c r="B20" s="31"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-    </row>
-    <row r="21" s="28" customFormat="1" spans="2:5">
-      <c r="B21" s="31"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-    </row>
-    <row r="22" s="28" customFormat="1" spans="2:5">
-      <c r="B22" s="31"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-    </row>
-    <row r="23" s="28" customFormat="1" spans="2:5">
-      <c r="B23" s="31"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-    </row>
-    <row r="24" s="28" customFormat="1" spans="2:5">
-      <c r="B24" s="31"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-    </row>
-    <row r="25" s="28" customFormat="1" spans="2:5">
-      <c r="B25" s="31"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-    </row>
-    <row r="26" s="28" customFormat="1" spans="2:5">
-      <c r="B26" s="31"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-    </row>
-    <row r="27" s="28" customFormat="1" spans="2:5">
-      <c r="B27" s="31"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-    </row>
-    <row r="28" s="28" customFormat="1" spans="2:5">
-      <c r="B28" s="31"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-    </row>
-    <row r="29" s="28" customFormat="1" spans="2:5">
-      <c r="B29" s="31"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-    </row>
-    <row r="30" s="28" customFormat="1" spans="2:5">
-      <c r="B30" s="31"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-    </row>
-    <row r="31" s="28" customFormat="1" spans="2:5">
-      <c r="B31" s="31"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-    </row>
-    <row r="32" s="28" customFormat="1" spans="2:5">
-      <c r="B32" s="31"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-    </row>
-    <row r="33" s="28" customFormat="1" spans="2:5">
-      <c r="B33" s="31"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-    </row>
-    <row r="34" s="28" customFormat="1" spans="2:5">
-      <c r="B34" s="31"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-    </row>
-    <row r="35" s="28" customFormat="1" spans="2:5">
-      <c r="B35" s="31"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-    </row>
-    <row r="36" s="28" customFormat="1" spans="2:5">
-      <c r="B36" s="31"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-    </row>
-    <row r="37" s="28" customFormat="1" spans="2:5">
-      <c r="B37" s="31"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-    </row>
-    <row r="38" s="28" customFormat="1" spans="2:5">
-      <c r="B38" s="31"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-    </row>
-    <row r="39" s="28" customFormat="1" spans="2:5">
-      <c r="B39" s="31"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-    </row>
-    <row r="40" s="28" customFormat="1" spans="2:5">
-      <c r="B40" s="31"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-    </row>
-    <row r="41" s="28" customFormat="1" spans="2:5">
-      <c r="B41" s="31"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-    </row>
-    <row r="42" s="28" customFormat="1" spans="2:5">
-      <c r="B42" s="31"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-    </row>
-    <row r="43" s="28" customFormat="1" spans="2:5">
-      <c r="B43" s="31"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-    </row>
-    <row r="44" s="28" customFormat="1" spans="2:5">
-      <c r="B44" s="31"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-    </row>
-    <row r="45" s="28" customFormat="1" spans="2:5">
-      <c r="B45" s="31"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-    </row>
-    <row r="46" s="28" customFormat="1" spans="2:5">
-      <c r="B46" s="31"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-    </row>
-    <row r="47" s="28" customFormat="1" spans="2:5">
-      <c r="B47" s="31"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-    </row>
-    <row r="48" s="28" customFormat="1" spans="2:5">
-      <c r="B48" s="31"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-    </row>
-    <row r="49" s="28" customFormat="1" spans="2:5">
-      <c r="B49" s="31"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-    </row>
-    <row r="50" s="28" customFormat="1" spans="2:5">
-      <c r="B50" s="31"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-    </row>
-    <row r="51" s="28" customFormat="1" spans="2:5">
-      <c r="B51" s="31"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-    </row>
-    <row r="52" s="28" customFormat="1" spans="2:5">
-      <c r="B52" s="31"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-    </row>
-    <row r="53" s="28" customFormat="1" spans="2:5">
-      <c r="B53" s="31"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-    </row>
-    <row r="54" s="28" customFormat="1" spans="2:5">
-      <c r="B54" s="31"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-    </row>
-    <row r="55" s="28" customFormat="1" spans="2:5">
-      <c r="B55" s="31"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-    </row>
-    <row r="56" s="28" customFormat="1" spans="2:5">
-      <c r="B56" s="31"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-    </row>
-    <row r="57" s="28" customFormat="1" spans="2:5">
-      <c r="B57" s="31"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
-    </row>
-    <row r="58" s="28" customFormat="1" spans="2:5">
-      <c r="B58" s="31"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-    </row>
-    <row r="59" s="28" customFormat="1" spans="2:5">
-      <c r="B59" s="31"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-    </row>
-    <row r="60" s="28" customFormat="1" spans="2:5">
-      <c r="B60" s="31"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-    </row>
-    <row r="61" s="28" customFormat="1" spans="2:5">
-      <c r="B61" s="31"/>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-    </row>
-    <row r="62" s="28" customFormat="1" spans="2:5">
-      <c r="B62" s="31"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-    </row>
-    <row r="63" s="28" customFormat="1" spans="2:5">
-      <c r="B63" s="31"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-    </row>
-    <row r="64" s="28" customFormat="1" spans="2:5">
-      <c r="B64" s="31"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
-    </row>
-    <row r="65" s="28" customFormat="1" spans="2:5">
-      <c r="B65" s="31"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
-    </row>
-    <row r="66" s="28" customFormat="1" spans="2:5">
-      <c r="B66" s="31"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-    </row>
-    <row r="67" s="28" customFormat="1" spans="2:5">
-      <c r="B67" s="31"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-    </row>
-    <row r="68" s="28" customFormat="1" spans="2:5">
-      <c r="B68" s="31"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="33"/>
-      <c r="E68" s="33"/>
+    <row r="5" s="30" customFormat="1" spans="2:5">
+      <c r="B5" s="33"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+    </row>
+    <row r="6" s="30" customFormat="1" spans="2:5">
+      <c r="B6" s="33"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+    </row>
+    <row r="7" s="30" customFormat="1" spans="2:5">
+      <c r="B7" s="33"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+    </row>
+    <row r="8" s="30" customFormat="1" spans="2:5">
+      <c r="B8" s="33"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+    </row>
+    <row r="9" s="30" customFormat="1" spans="2:5">
+      <c r="B9" s="33"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+    </row>
+    <row r="10" s="30" customFormat="1" spans="2:5">
+      <c r="B10" s="33"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11" s="30" customFormat="1" spans="2:5">
+      <c r="B11" s="33"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12" s="30" customFormat="1" spans="2:5">
+      <c r="B12" s="33"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+    </row>
+    <row r="13" s="30" customFormat="1" spans="2:5">
+      <c r="B13" s="33"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+    </row>
+    <row r="14" s="30" customFormat="1" spans="2:5">
+      <c r="B14" s="33"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" s="30" customFormat="1" spans="2:5">
+      <c r="B15" s="33"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" s="30" customFormat="1" spans="2:5">
+      <c r="B16" s="33"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+    </row>
+    <row r="17" s="30" customFormat="1" spans="2:5">
+      <c r="B17" s="33"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+    </row>
+    <row r="18" s="30" customFormat="1" spans="2:5">
+      <c r="B18" s="33"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+    </row>
+    <row r="19" s="30" customFormat="1" spans="2:5">
+      <c r="B19" s="33"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+    </row>
+    <row r="20" s="30" customFormat="1" spans="2:5">
+      <c r="B20" s="33"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+    </row>
+    <row r="21" s="30" customFormat="1" spans="2:5">
+      <c r="B21" s="33"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+    </row>
+    <row r="22" s="30" customFormat="1" spans="2:5">
+      <c r="B22" s="33"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+    </row>
+    <row r="23" s="30" customFormat="1" spans="2:5">
+      <c r="B23" s="33"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+    </row>
+    <row r="24" s="30" customFormat="1" spans="2:5">
+      <c r="B24" s="33"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+    </row>
+    <row r="25" s="30" customFormat="1" spans="2:5">
+      <c r="B25" s="33"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+    </row>
+    <row r="26" s="30" customFormat="1" spans="2:5">
+      <c r="B26" s="33"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+    </row>
+    <row r="27" s="30" customFormat="1" spans="2:5">
+      <c r="B27" s="33"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+    </row>
+    <row r="28" s="30" customFormat="1" spans="2:5">
+      <c r="B28" s="33"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+    </row>
+    <row r="29" s="30" customFormat="1" spans="2:5">
+      <c r="B29" s="33"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+    </row>
+    <row r="30" s="30" customFormat="1" spans="2:5">
+      <c r="B30" s="33"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+    </row>
+    <row r="31" s="30" customFormat="1" spans="2:5">
+      <c r="B31" s="33"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+    </row>
+    <row r="32" s="30" customFormat="1" spans="2:5">
+      <c r="B32" s="33"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+    </row>
+    <row r="33" s="30" customFormat="1" spans="2:5">
+      <c r="B33" s="33"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+    </row>
+    <row r="34" s="30" customFormat="1" spans="2:5">
+      <c r="B34" s="33"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+    </row>
+    <row r="35" s="30" customFormat="1" spans="2:5">
+      <c r="B35" s="33"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+    </row>
+    <row r="36" s="30" customFormat="1" spans="2:5">
+      <c r="B36" s="33"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+    </row>
+    <row r="37" s="30" customFormat="1" spans="2:5">
+      <c r="B37" s="33"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+    </row>
+    <row r="38" s="30" customFormat="1" spans="2:5">
+      <c r="B38" s="33"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+    </row>
+    <row r="39" s="30" customFormat="1" spans="2:5">
+      <c r="B39" s="33"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+    </row>
+    <row r="40" s="30" customFormat="1" spans="2:5">
+      <c r="B40" s="33"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+    </row>
+    <row r="41" s="30" customFormat="1" spans="2:5">
+      <c r="B41" s="33"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+    </row>
+    <row r="42" s="30" customFormat="1" spans="2:5">
+      <c r="B42" s="33"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+    </row>
+    <row r="43" s="30" customFormat="1" spans="2:5">
+      <c r="B43" s="33"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+    </row>
+    <row r="44" s="30" customFormat="1" spans="2:5">
+      <c r="B44" s="33"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+    </row>
+    <row r="45" s="30" customFormat="1" spans="2:5">
+      <c r="B45" s="33"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+    </row>
+    <row r="46" s="30" customFormat="1" spans="2:5">
+      <c r="B46" s="33"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+    </row>
+    <row r="47" s="30" customFormat="1" spans="2:5">
+      <c r="B47" s="33"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+    </row>
+    <row r="48" s="30" customFormat="1" spans="2:5">
+      <c r="B48" s="33"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+    </row>
+    <row r="49" s="30" customFormat="1" spans="2:5">
+      <c r="B49" s="33"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+    </row>
+    <row r="50" s="30" customFormat="1" spans="2:5">
+      <c r="B50" s="33"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+    </row>
+    <row r="51" s="30" customFormat="1" spans="2:5">
+      <c r="B51" s="33"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+    </row>
+    <row r="52" s="30" customFormat="1" spans="2:5">
+      <c r="B52" s="33"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+    </row>
+    <row r="53" s="30" customFormat="1" spans="2:5">
+      <c r="B53" s="33"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+    </row>
+    <row r="54" s="30" customFormat="1" spans="2:5">
+      <c r="B54" s="33"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+    </row>
+    <row r="55" s="30" customFormat="1" spans="2:5">
+      <c r="B55" s="33"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+    </row>
+    <row r="56" s="30" customFormat="1" spans="2:5">
+      <c r="B56" s="33"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+    </row>
+    <row r="57" s="30" customFormat="1" spans="2:5">
+      <c r="B57" s="33"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+    </row>
+    <row r="58" s="30" customFormat="1" spans="2:5">
+      <c r="B58" s="33"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+    </row>
+    <row r="59" s="30" customFormat="1" spans="2:5">
+      <c r="B59" s="33"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+    </row>
+    <row r="60" s="30" customFormat="1" spans="2:5">
+      <c r="B60" s="33"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+    </row>
+    <row r="61" s="30" customFormat="1" spans="2:5">
+      <c r="B61" s="33"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+    </row>
+    <row r="62" s="30" customFormat="1" spans="2:5">
+      <c r="B62" s="33"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+    </row>
+    <row r="63" s="30" customFormat="1" spans="2:5">
+      <c r="B63" s="33"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+    </row>
+    <row r="64" s="30" customFormat="1" spans="2:5">
+      <c r="B64" s="33"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+    </row>
+    <row r="65" s="30" customFormat="1" spans="2:5">
+      <c r="B65" s="33"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+    </row>
+    <row r="66" s="30" customFormat="1" spans="2:5">
+      <c r="B66" s="33"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+    </row>
+    <row r="67" s="30" customFormat="1" spans="2:5">
+      <c r="B67" s="33"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="35"/>
+    </row>
+    <row r="68" s="30" customFormat="1" spans="2:5">
+      <c r="B68" s="33"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2071,17 +2083,17 @@
       <c r="V1" s="15"/>
       <c r="W1" s="15"/>
       <c r="X1" s="15"/>
-      <c r="Y1" s="27" t="s">
+      <c r="Y1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="19" t="s">
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AB1" s="27" t="s">
+      <c r="AB1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="35" t="s">
+      <c r="AC1" s="37" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2110,10 +2122,10 @@
       <c r="V2" s="15"/>
       <c r="W2" s="15"/>
       <c r="X2" s="15"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="27"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="29"/>
       <c r="AC2" s="7"/>
     </row>
     <row r="3" customHeight="1" spans="1:29">
@@ -2143,15 +2155,15 @@
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
-      <c r="Y3" s="27" t="s">
+      <c r="Y3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="27" t="s">
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="AC3" s="19"/>
+      <c r="AC3" s="21"/>
     </row>
     <row r="4" customHeight="1" spans="1:29">
       <c r="A4" s="2"/>
@@ -2178,11 +2190,11 @@
       <c r="V4" s="7"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="19"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="21"/>
     </row>
     <row r="5" customHeight="1" spans="1:29">
       <c r="A5" s="3" t="s">
@@ -2229,40 +2241,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="23" t="str">
+      <c r="C6" s="25" t="str">
         <f>HYPERLINK("#'admin_info'!A1","admin_info")</f>
         <v>admin_info</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23" t="s">
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
-      <c r="AC6" s="23"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
     </row>
     <row r="7" customHeight="1" spans="1:29">
       <c r="A7" s="7">
@@ -2270,39 +2282,39 @@
         <v>2</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23" t="s">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
-      <c r="AC7" s="23"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
     </row>
     <row r="8" customHeight="1" spans="1:29">
       <c r="A8" s="7">
@@ -2310,39 +2322,39 @@
         <v>3</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23" t="s">
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23" t="s">
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="23"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
     </row>
     <row r="9" customHeight="1" spans="1:29">
       <c r="A9" s="7">
@@ -2350,39 +2362,39 @@
         <v>4</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23" t="s">
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23" t="s">
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
     </row>
     <row r="10" customHeight="1" spans="1:29">
       <c r="A10" s="7">
@@ -2390,101 +2402,101 @@
         <v>5</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23" t="s">
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23" t="s">
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="23"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
     </row>
     <row r="11" customHeight="1" spans="1:29">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="23"/>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
-      <c r="AC11" s="23"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
     </row>
     <row r="12" customHeight="1" spans="1:29">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="24"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
-      <c r="AC12" s="23"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
     </row>
     <row r="13" customHeight="1" spans="1:29">
       <c r="A13" s="7"/>
@@ -2503,19 +2515,19 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
     </row>
     <row r="14" customHeight="1" spans="1:29">
       <c r="A14" s="7"/>
@@ -2534,19 +2546,19 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
     </row>
     <row r="15" customHeight="1" spans="1:29">
       <c r="A15" s="7"/>
@@ -2565,19 +2577,19 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="23"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
     </row>
     <row r="16" customHeight="1" spans="1:29">
       <c r="A16" s="7"/>
@@ -2596,19 +2608,19 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="23"/>
-      <c r="AB16" s="23"/>
-      <c r="AC16" s="23"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
     </row>
     <row r="17" customHeight="1" spans="1:29">
       <c r="A17" s="7"/>
@@ -2627,19 +2639,19 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="23"/>
-      <c r="AC17" s="23"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
     </row>
     <row r="18" customHeight="1" spans="1:29">
       <c r="A18" s="7"/>
@@ -2658,19 +2670,19 @@
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
-      <c r="AA18" s="23"/>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="23"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
     </row>
     <row r="19" customHeight="1" spans="1:29">
       <c r="A19" s="7"/>
@@ -2689,19 +2701,19 @@
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="23"/>
-      <c r="AA19" s="23"/>
-      <c r="AB19" s="23"/>
-      <c r="AC19" s="23"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
     </row>
     <row r="20" customHeight="1" spans="1:29">
       <c r="A20" s="7"/>
@@ -2720,19 +2732,19 @@
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="23"/>
-      <c r="AA20" s="23"/>
-      <c r="AB20" s="23"/>
-      <c r="AC20" s="23"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
     </row>
     <row r="21" customHeight="1" spans="1:29">
       <c r="A21" s="7"/>
@@ -2751,19 +2763,19 @@
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
-      <c r="AC21" s="23"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
     </row>
     <row r="22" customHeight="1" spans="1:29">
       <c r="A22" s="7"/>
@@ -2782,19 +2794,19 @@
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="23"/>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
-      <c r="AC22" s="23"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
     </row>
     <row r="23" customHeight="1" spans="1:29">
       <c r="A23" s="7"/>
@@ -2813,19 +2825,19 @@
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="23"/>
-      <c r="AA23" s="23"/>
-      <c r="AB23" s="23"/>
-      <c r="AC23" s="23"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
     </row>
     <row r="24" customHeight="1" spans="1:29">
       <c r="A24" s="7"/>
@@ -2844,19 +2856,19 @@
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="23"/>
-      <c r="AA24" s="23"/>
-      <c r="AB24" s="23"/>
-      <c r="AC24" s="23"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
     </row>
     <row r="25" customHeight="1" spans="1:29">
       <c r="A25" s="7"/>
@@ -2875,19 +2887,19 @@
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="23"/>
-      <c r="AA25" s="23"/>
-      <c r="AB25" s="23"/>
-      <c r="AC25" s="23"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
     </row>
     <row r="26" customHeight="1" spans="1:29">
       <c r="A26" s="7"/>
@@ -2906,19 +2918,19 @@
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
-      <c r="AA26" s="23"/>
-      <c r="AB26" s="23"/>
-      <c r="AC26" s="23"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
     </row>
     <row r="27" customHeight="1" spans="1:29">
       <c r="A27" s="7"/>
@@ -2937,19 +2949,19 @@
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="23"/>
-      <c r="AB27" s="23"/>
-      <c r="AC27" s="23"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
     </row>
     <row r="28" customHeight="1" spans="1:29">
       <c r="A28" s="7"/>
@@ -2968,19 +2980,19 @@
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
       <c r="P28" s="7"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="23"/>
-      <c r="AA28" s="23"/>
-      <c r="AB28" s="23"/>
-      <c r="AC28" s="23"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+      <c r="AC28" s="25"/>
     </row>
     <row r="29" customHeight="1" spans="1:29">
       <c r="A29" s="7"/>
@@ -2999,19 +3011,19 @@
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
       <c r="P29" s="7"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="23"/>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="23"/>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="23"/>
-      <c r="AA29" s="23"/>
-      <c r="AB29" s="23"/>
-      <c r="AC29" s="23"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="25"/>
     </row>
     <row r="30" customHeight="1" spans="1:29">
       <c r="A30" s="7"/>
@@ -3030,19 +3042,19 @@
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="23"/>
-      <c r="AB30" s="23"/>
-      <c r="AC30" s="23"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+      <c r="AC30" s="25"/>
     </row>
     <row r="31" customHeight="1" spans="1:29">
       <c r="A31" s="7"/>
@@ -3061,19 +3073,19 @@
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="26"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
+      <c r="V31" s="28"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+      <c r="AC31" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="119">
@@ -3253,16 +3265,16 @@
       </c>
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
-      <c r="AA1" s="19" t="s">
+      <c r="AA1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
       <c r="AE1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AF1" s="35" t="s">
+      <c r="AF1" s="37" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3295,10 +3307,10 @@
       <c r="X2" s="15"/>
       <c r="Y2" s="15"/>
       <c r="Z2" s="15"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
       <c r="AE2" s="15"/>
       <c r="AF2" s="7"/>
     </row>
@@ -3448,20 +3460,20 @@
         <v>1</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23" t="s">
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="7" t="s">
         <v>53</v>
       </c>
@@ -3483,15 +3495,15 @@
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="20"/>
-      <c r="AD6" s="20"/>
-      <c r="AE6" s="23" t="s">
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="AF6" s="23"/>
+      <c r="AF6" s="25"/>
     </row>
     <row r="7" customHeight="1" spans="1:32">
       <c r="A7" s="7">
@@ -3499,20 +3511,20 @@
         <v>2</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="7" t="s">
         <v>53</v>
       </c>
@@ -3532,15 +3544,15 @@
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="20"/>
-      <c r="AE7" s="23" t="s">
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
+      <c r="AE7" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="AF7" s="23"/>
+      <c r="AF7" s="25"/>
     </row>
     <row r="8" customHeight="1" spans="1:32">
       <c r="A8" s="7">
@@ -3548,20 +3560,20 @@
         <v>3</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23" t="s">
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
       <c r="M8" s="7" t="s">
         <v>53</v>
       </c>
@@ -3581,15 +3593,15 @@
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
-      <c r="AE8" s="23" t="s">
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
+      <c r="AE8" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="AF8" s="23"/>
+      <c r="AF8" s="25"/>
     </row>
     <row r="9" customHeight="1" spans="1:32">
       <c r="A9" s="7">
@@ -3597,20 +3609,20 @@
         <v>4</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23" t="s">
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
       <c r="M9" s="7" t="s">
         <v>53</v>
       </c>
@@ -3630,15 +3642,15 @@
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="23" t="s">
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="AF9" s="23"/>
+      <c r="AF9" s="25"/>
     </row>
     <row r="10" customHeight="1" spans="1:32">
       <c r="A10" s="7">
@@ -3646,20 +3658,20 @@
         <v>5</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23" t="s">
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
       <c r="M10" s="7" t="s">
         <v>53</v>
       </c>
@@ -3679,15 +3691,15 @@
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
-      <c r="AE10" s="23" t="s">
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="AF10" s="23"/>
+      <c r="AF10" s="25"/>
     </row>
     <row r="11" customHeight="1" spans="1:32">
       <c r="A11" s="7">
@@ -3695,20 +3707,20 @@
         <v>6</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23" t="s">
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
       <c r="M11" s="7" t="s">
         <v>70</v>
       </c>
@@ -3728,15 +3740,15 @@
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="20"/>
-      <c r="AE11" s="23" t="s">
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="AF11" s="23"/>
+      <c r="AF11" s="25"/>
     </row>
     <row r="12" customHeight="1" spans="1:32">
       <c r="A12" s="7">
@@ -3744,20 +3756,20 @@
         <v>7</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23" t="s">
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
       <c r="M12" s="7" t="s">
         <v>74</v>
       </c>
@@ -3775,15 +3787,15 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
-      <c r="AE12" s="23" t="s">
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
+      <c r="AE12" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="AF12" s="23"/>
+      <c r="AF12" s="25"/>
     </row>
     <row r="13" customHeight="1" spans="1:32">
       <c r="A13" s="7">
@@ -3791,20 +3803,20 @@
         <v>8</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23" t="s">
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
       <c r="M13" s="7" t="s">
         <v>74</v>
       </c>
@@ -3822,15 +3834,15 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
-      <c r="AE13" s="23" t="s">
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="AF13" s="23"/>
+      <c r="AF13" s="25"/>
     </row>
     <row r="14" customHeight="1" spans="1:32">
       <c r="A14" s="7"/>
@@ -3858,11 +3870,11 @@
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
     </row>
@@ -3892,11 +3904,11 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
     </row>
@@ -3926,11 +3938,11 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
     </row>
@@ -3960,11 +3972,11 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
     </row>
@@ -3994,11 +4006,11 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
     </row>
@@ -4028,11 +4040,11 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="20"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
     </row>
@@ -4062,11 +4074,11 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
     </row>
@@ -4096,11 +4108,11 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
     </row>
@@ -4130,11 +4142,11 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
     </row>
@@ -4164,11 +4176,11 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
     </row>
@@ -4198,11 +4210,11 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
     </row>
@@ -4232,11 +4244,11 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
     </row>
@@ -4266,11 +4278,11 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
     </row>
@@ -4300,11 +4312,11 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
     </row>
@@ -4334,11 +4346,11 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="20"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
     </row>
@@ -4368,11 +4380,11 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
     </row>
@@ -4402,11 +4414,11 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
-      <c r="AC30" s="20"/>
-      <c r="AD30" s="20"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
     </row>
@@ -4436,11 +4448,11 @@
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="20"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
     </row>
@@ -4470,11 +4482,11 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
-      <c r="AC32" s="20"/>
-      <c r="AD32" s="20"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
       <c r="AE32" s="10"/>
       <c r="AF32" s="16"/>
     </row>
@@ -4504,11 +4516,11 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
     </row>
@@ -4845,16 +4857,16 @@
       </c>
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
-      <c r="AA1" s="19" t="s">
+      <c r="AA1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
       <c r="AE1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AF1" s="35" t="s">
+      <c r="AF1" s="37" t="s">
         <v>13</v>
       </c>
       <c r="XEU1"/>
@@ -4888,10 +4900,10 @@
       <c r="X2" s="15"/>
       <c r="Y2" s="15"/>
       <c r="Z2" s="15"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
       <c r="AE2" s="15"/>
       <c r="AF2" s="7"/>
       <c r="XEU2"/>
@@ -5079,11 +5091,11 @@
         <v>54</v>
       </c>
       <c r="Y6" s="13"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="20"/>
-      <c r="AD6" s="20"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
       <c r="AE6" s="6" t="s">
         <v>82</v>
       </c>
@@ -5128,11 +5140,11 @@
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="20"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
       <c r="AE7" s="6" t="s">
         <v>84</v>
       </c>
@@ -5177,11 +5189,11 @@
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
       <c r="AE8" s="6" t="s">
         <v>71</v>
       </c>
@@ -5224,11 +5236,11 @@
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
       <c r="AE9" s="6" t="s">
         <v>75</v>
       </c>
@@ -5271,15 +5283,15 @@
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
-      <c r="AE10" s="21" t="s">
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="AF10" s="22"/>
+      <c r="AF10" s="24"/>
       <c r="XEU10"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:16375">
@@ -5308,11 +5320,11 @@
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="20"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
       <c r="XEU11"/>
@@ -5343,11 +5355,11 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
       <c r="XEU12"/>
@@ -5378,11 +5390,11 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
       <c r="XEU13"/>
@@ -5413,11 +5425,11 @@
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
       <c r="XEU14"/>
@@ -5448,11 +5460,11 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
       <c r="XEU15"/>
@@ -5483,11 +5495,11 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
       <c r="XEU16"/>
@@ -5518,11 +5530,11 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
       <c r="XEU17"/>
@@ -5553,11 +5565,11 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
       <c r="XEU18"/>
@@ -5588,11 +5600,11 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="20"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
       <c r="XEU19"/>
@@ -5623,11 +5635,11 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
       <c r="XEU20"/>
@@ -5658,11 +5670,11 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
       <c r="XEU21"/>
@@ -5693,11 +5705,11 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
       <c r="XEU22"/>
@@ -5728,11 +5740,11 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
       <c r="XEU23"/>
@@ -5763,11 +5775,11 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
       <c r="XEU24"/>
@@ -5798,11 +5810,11 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
       <c r="XEU25"/>
@@ -5833,11 +5845,11 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
       <c r="XEU26"/>
@@ -5868,11 +5880,11 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
       <c r="XEU27"/>
@@ -5903,11 +5915,11 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="20"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
       <c r="XEU28"/>
@@ -5938,11 +5950,11 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
       <c r="XEU29"/>
@@ -5973,11 +5985,11 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
-      <c r="AC30" s="20"/>
-      <c r="AD30" s="20"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
       <c r="XEU30"/>
@@ -6008,11 +6020,11 @@
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="20"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
       <c r="XEU31"/>
@@ -6043,11 +6055,11 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
-      <c r="AC32" s="20"/>
-      <c r="AD32" s="20"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
       <c r="AE32" s="10"/>
       <c r="AF32" s="16"/>
       <c r="XEU32"/>
@@ -6078,11 +6090,11 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
       <c r="XEU33"/>
@@ -6420,16 +6432,16 @@
       </c>
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
-      <c r="AA1" s="19" t="s">
+      <c r="AA1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
       <c r="AE1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AF1" s="35" t="s">
+      <c r="AF1" s="37" t="s">
         <v>13</v>
       </c>
       <c r="XEU1"/>
@@ -6463,10 +6475,10 @@
       <c r="X2" s="15"/>
       <c r="Y2" s="15"/>
       <c r="Z2" s="15"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
       <c r="AE2" s="15"/>
       <c r="AF2" s="7"/>
       <c r="XEU2"/>
@@ -6654,11 +6666,11 @@
         <v>54</v>
       </c>
       <c r="Y6" s="13"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="20"/>
-      <c r="AD6" s="20"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
       <c r="AE6" s="6" t="s">
         <v>88</v>
       </c>
@@ -6703,11 +6715,11 @@
       <c r="W7" s="13"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="13"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="20"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
       <c r="AE7" s="6" t="s">
         <v>90</v>
       </c>
@@ -6752,11 +6764,11 @@
       <c r="W8" s="13"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="13"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
       <c r="AE8" s="6" t="s">
         <v>93</v>
       </c>
@@ -6801,11 +6813,11 @@
       <c r="W9" s="13"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="13"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
       <c r="AE9" s="6" t="s">
         <v>96</v>
       </c>
@@ -6850,11 +6862,11 @@
       <c r="W10" s="13"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="13"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
       <c r="AE10" s="6" t="s">
         <v>97</v>
       </c>
@@ -6899,11 +6911,11 @@
       <c r="W11" s="13"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="13"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="20"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
       <c r="AE11" s="6" t="s">
         <v>100</v>
       </c>
@@ -6948,11 +6960,11 @@
       <c r="W12" s="13"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="13"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
       <c r="AE12" s="6" t="s">
         <v>103</v>
       </c>
@@ -6995,11 +7007,11 @@
       <c r="W13" s="13"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="13"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
       <c r="AE13" s="6" t="s">
         <v>106</v>
       </c>
@@ -7042,11 +7054,11 @@
       <c r="W14" s="13"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="13"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
       <c r="AE14" s="6" t="s">
         <v>109</v>
       </c>
@@ -7089,15 +7101,15 @@
       <c r="W15" s="13"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="13"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="21" t="s">
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
+      <c r="AE15" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="AF15" s="22"/>
+      <c r="AF15" s="24"/>
       <c r="XEU15"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:16375">
@@ -7138,11 +7150,11 @@
       <c r="W16" s="13"/>
       <c r="X16" s="5"/>
       <c r="Y16" s="13"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
       <c r="AE16" s="6" t="s">
         <v>71</v>
       </c>
@@ -7185,11 +7197,11 @@
       <c r="W17" s="13"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="13"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
       <c r="AE17" s="6" t="s">
         <v>75</v>
       </c>
@@ -7232,15 +7244,15 @@
       <c r="W18" s="13"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="13"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
-      <c r="AE18" s="21" t="s">
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="AF18" s="22"/>
+      <c r="AF18" s="24"/>
       <c r="XEU18"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:16375">
@@ -7269,11 +7281,11 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="20"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
       <c r="XEU19"/>
@@ -7304,11 +7316,11 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
       <c r="XEU20"/>
@@ -7339,11 +7351,11 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
       <c r="XEU21"/>
@@ -7374,11 +7386,11 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
       <c r="XEU22"/>
@@ -7409,11 +7421,11 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
       <c r="XEU23"/>
@@ -7444,11 +7456,11 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
       <c r="XEU24"/>
@@ -7479,11 +7491,11 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
       <c r="XEU25"/>
@@ -7514,11 +7526,11 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
       <c r="XEU26"/>
@@ -7549,11 +7561,11 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
       <c r="XEU27"/>
@@ -7584,11 +7596,11 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="20"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
       <c r="XEU28"/>
@@ -7619,11 +7631,11 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
       <c r="XEU29"/>
@@ -7654,11 +7666,11 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
-      <c r="AC30" s="20"/>
-      <c r="AD30" s="20"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
       <c r="XEU30"/>
@@ -7689,11 +7701,11 @@
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="20"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
       <c r="XEU31"/>
@@ -7724,11 +7736,11 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
-      <c r="AC32" s="20"/>
-      <c r="AD32" s="20"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
       <c r="AE32" s="10"/>
       <c r="AF32" s="16"/>
       <c r="XEU32"/>
@@ -7759,11 +7771,11 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
       <c r="XEU33"/>
@@ -8101,16 +8113,16 @@
       </c>
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
-      <c r="AA1" s="19" t="s">
+      <c r="AA1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
       <c r="AE1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AF1" s="35" t="s">
+      <c r="AF1" s="37" t="s">
         <v>13</v>
       </c>
       <c r="XEU1"/>
@@ -8144,10 +8156,10 @@
       <c r="X2" s="15"/>
       <c r="Y2" s="15"/>
       <c r="Z2" s="15"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
       <c r="AE2" s="15"/>
       <c r="AF2" s="7"/>
       <c r="XEU2"/>
@@ -8335,11 +8347,11 @@
         <v>54</v>
       </c>
       <c r="Y6" s="13"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="20"/>
-      <c r="AD6" s="20"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
       <c r="AE6" s="6" t="s">
         <v>88</v>
       </c>
@@ -8386,11 +8398,11 @@
       <c r="W7" s="13"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="13"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="20"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
       <c r="AE7" s="6" t="s">
         <v>115</v>
       </c>
@@ -8435,11 +8447,11 @@
       <c r="W8" s="13"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="13"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
       <c r="AE8" s="6" t="s">
         <v>118</v>
       </c>
@@ -8484,11 +8496,11 @@
       <c r="W9" s="13"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="13"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
       <c r="AE9" s="6" t="s">
         <v>121</v>
       </c>
@@ -8533,11 +8545,11 @@
       <c r="W10" s="13"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="13"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
       <c r="AE10" s="6" t="s">
         <v>124</v>
       </c>
@@ -8580,11 +8592,11 @@
       <c r="W11" s="13"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="13"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="20"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
       <c r="AE11" s="6" t="s">
         <v>127</v>
       </c>
@@ -8629,11 +8641,11 @@
       <c r="W12" s="13"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="13"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
       <c r="AE12" s="6" t="s">
         <v>71</v>
       </c>
@@ -8676,11 +8688,11 @@
       <c r="W13" s="13"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="13"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
       <c r="AE13" s="6" t="s">
         <v>75</v>
       </c>
@@ -8723,15 +8735,15 @@
       <c r="W14" s="13"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="13"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="21" t="s">
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="AF14" s="22"/>
+      <c r="AF14" s="24"/>
       <c r="XEU14"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:16375">
@@ -8760,11 +8772,11 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
       <c r="XEU15"/>
@@ -8795,11 +8807,11 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
       <c r="XEU16"/>
@@ -8830,11 +8842,11 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
       <c r="XEU17"/>
@@ -8865,11 +8877,11 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
       <c r="XEU18"/>
@@ -8900,11 +8912,11 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="20"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
       <c r="XEU19"/>
@@ -8935,11 +8947,11 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
       <c r="XEU20"/>
@@ -8970,11 +8982,11 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
       <c r="XEU21"/>
@@ -9005,11 +9017,11 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
       <c r="XEU22"/>
@@ -9040,11 +9052,11 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
       <c r="XEU23"/>
@@ -9075,11 +9087,11 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
       <c r="XEU24"/>
@@ -9110,11 +9122,11 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
       <c r="XEU25"/>
@@ -9145,11 +9157,11 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
       <c r="XEU26"/>
@@ -9180,11 +9192,11 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
       <c r="XEU27"/>
@@ -9215,11 +9227,11 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="20"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
       <c r="XEU28"/>
@@ -9250,11 +9262,11 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
       <c r="XEU29"/>
@@ -9285,11 +9297,11 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
-      <c r="AC30" s="20"/>
-      <c r="AD30" s="20"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
       <c r="XEU30"/>
@@ -9320,11 +9332,11 @@
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="20"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
       <c r="XEU31"/>
@@ -9355,11 +9367,11 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
-      <c r="AC32" s="20"/>
-      <c r="AD32" s="20"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
       <c r="AE32" s="10"/>
       <c r="AF32" s="16"/>
       <c r="XEU32"/>
@@ -9390,11 +9402,11 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
       <c r="XEU33"/>
@@ -9732,16 +9744,16 @@
       </c>
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
-      <c r="AA1" s="19" t="s">
+      <c r="AA1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
       <c r="AE1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AF1" s="35" t="s">
+      <c r="AF1" s="37" t="s">
         <v>13</v>
       </c>
       <c r="XEU1"/>
@@ -9775,10 +9787,10 @@
       <c r="X2" s="15"/>
       <c r="Y2" s="15"/>
       <c r="Z2" s="15"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
       <c r="AE2" s="15"/>
       <c r="AF2" s="7"/>
       <c r="XEU2"/>
@@ -9966,11 +9978,11 @@
         <v>54</v>
       </c>
       <c r="Y6" s="13"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="20"/>
-      <c r="AD6" s="20"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
       <c r="AE6" s="6" t="s">
         <v>88</v>
       </c>
@@ -10015,11 +10027,11 @@
       <c r="W7" s="13"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="13"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="20"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
       <c r="AE7" s="6" t="s">
         <v>130</v>
       </c>
@@ -10056,19 +10068,19 @@
       </c>
       <c r="R8" s="13"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="5" t="s">
+      <c r="T8" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="U8" s="13"/>
+      <c r="U8" s="20"/>
       <c r="V8" s="5"/>
       <c r="W8" s="13"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="13"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
       <c r="AE8" s="6" t="s">
         <v>132</v>
       </c>
@@ -10113,11 +10125,11 @@
       <c r="W9" s="13"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="13"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
       <c r="AE9" s="6" t="s">
         <v>133</v>
       </c>
@@ -10160,11 +10172,11 @@
       <c r="W10" s="13"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="13"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
       <c r="AE10" s="6" t="s">
         <v>136</v>
       </c>
@@ -10207,11 +10219,11 @@
       <c r="W11" s="13"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="13"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="20"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
       <c r="AE11" s="6" t="s">
         <v>139</v>
       </c>
@@ -10256,11 +10268,11 @@
       <c r="W12" s="13"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="13"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
       <c r="AE12" s="6" t="s">
         <v>71</v>
       </c>
@@ -10303,11 +10315,11 @@
       <c r="W13" s="13"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="13"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
       <c r="AE13" s="6" t="s">
         <v>140</v>
       </c>
@@ -10350,15 +10362,15 @@
       <c r="W14" s="13"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="13"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="21" t="s">
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AF14" s="22"/>
+      <c r="AF14" s="24"/>
       <c r="XEU14"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:16375">
@@ -10387,11 +10399,11 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
       <c r="XEU15"/>
@@ -10422,11 +10434,11 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
       <c r="XEU16"/>
@@ -10457,11 +10469,11 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
       <c r="XEU17"/>
@@ -10492,11 +10504,11 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
       <c r="XEU18"/>
@@ -10527,11 +10539,11 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="20"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
       <c r="XEU19"/>
@@ -10562,11 +10574,11 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
       <c r="XEU20"/>
@@ -10597,11 +10609,11 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
       <c r="XEU21"/>
@@ -10632,11 +10644,11 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
       <c r="XEU22"/>
@@ -10667,11 +10679,11 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
       <c r="XEU23"/>
@@ -10702,11 +10714,11 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
       <c r="XEU24"/>
@@ -10737,11 +10749,11 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
       <c r="XEU25"/>
@@ -10772,11 +10784,11 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
       <c r="XEU26"/>
@@ -10807,11 +10819,11 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
       <c r="XEU27"/>
@@ -10842,11 +10854,11 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="20"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
       <c r="XEU28"/>
@@ -10877,11 +10889,11 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
       <c r="XEU29"/>
@@ -10912,11 +10924,11 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
-      <c r="AC30" s="20"/>
-      <c r="AD30" s="20"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
       <c r="XEU30"/>
@@ -10947,11 +10959,11 @@
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="20"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
       <c r="XEU31"/>
@@ -10982,11 +10994,11 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
-      <c r="AC32" s="20"/>
-      <c r="AD32" s="20"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
       <c r="AE32" s="10"/>
       <c r="AF32" s="16"/>
       <c r="XEU32"/>
@@ -11017,11 +11029,11 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
       <c r="XEU33"/>

--- a/docs/詳細設計書/テーブル定義書.xlsx
+++ b/docs/詳細設計書/テーブル定義書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7575"/>
+    <workbookView windowWidth="28125" windowHeight="14055" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="18" r:id="rId1"/>
@@ -387,7 +387,7 @@
     <t>操作を行ったテーブルのID（外部キー）</t>
   </si>
   <si>
-    <t>operation_type</t>
+    <t>operate_type</t>
   </si>
   <si>
     <t>操作種類</t>
@@ -461,10 +461,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -522,73 +522,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -610,6 +544,14 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
@@ -617,8 +559,73 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -648,13 +655,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -671,7 +671,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,19 +683,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,85 +785,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,13 +809,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,25 +839,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,16 +912,34 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -941,35 +959,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1016,145 +1016,145 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/docs/詳細設計書/テーブル定義書.xlsx
+++ b/docs/詳細設計書/テーブル定義書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="14055" activeTab="5"/>
+    <workbookView windowWidth="28125" windowHeight="14055" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="18" r:id="rId1"/>
@@ -461,10 +461,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -514,46 +514,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -567,14 +535,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -588,7 +549,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -596,7 +557,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -611,7 +596,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -625,10 +610,33 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -641,18 +649,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -671,7 +671,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -683,31 +683,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,7 +737,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -737,61 +773,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -803,7 +803,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -815,13 +815,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,19 +827,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,16 +912,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -937,24 +937,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -974,6 +976,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -983,27 +1000,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1013,148 +1013,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2037,6 +2037,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>

--- a/docs/詳細設計書/テーブル定義書.xlsx
+++ b/docs/詳細設計書/テーブル定義書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="14055" activeTab="2"/>
+    <workbookView windowWidth="19815" windowHeight="7575"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="18" r:id="rId1"/>
@@ -53,9 +53,9 @@
   </si>
   <si>
     <t>◆stock_info
-nameをNOT NULLに変更。
+　・nameをNOT NULLに変更。
 ◆operation_log
-log_idのみを主キーに変更 (status を主キーから削除)</t>
+　・log_idのみを主キーに変更 (status を主キーから削除)</t>
   </si>
   <si>
     <t>テーブル一覧</t>
@@ -462,9 +462,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -514,28 +514,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -549,7 +565,38 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -557,7 +604,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -587,46 +641,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -634,25 +650,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -671,67 +671,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,55 +689,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -809,6 +707,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -821,13 +767,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -839,13 +827,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,6 +912,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -922,6 +946,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -960,201 +1008,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1268,7 +1268,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1637,7 +1637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="30" customFormat="1" ht="66" spans="2:5">
+    <row r="4" s="30" customFormat="1" ht="80" customHeight="1" spans="2:5">
       <c r="B4" s="33" t="s">
         <v>8</v>
       </c>
